--- a/HistoriasUsuario.xlsx
+++ b/HistoriasUsuario.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="280">
   <si>
     <t>Historias de Usuario y criterios de aceptación de HE-01</t>
   </si>
@@ -29,12 +29,6 @@
   </si>
   <si>
     <t>Criterios de aceptación</t>
-  </si>
-  <si>
-    <t>Vista navegador</t>
-  </si>
-  <si>
-    <t>Vista Movil</t>
   </si>
   <si>
     <t>Identificador (ID) de la épica</t>
@@ -85,67 +79,70 @@
     <t>Agendamiento exitoso</t>
   </si>
   <si>
-    <t>En caso de entrar a agendar cita y seleccionar un horario y médico de los indicados en las opciones con disponibilidad</t>
+    <t xml:space="preserve">Dado que estando en el panel de Paciente (P5 Path: Menú Paciente), en caso de entrar a agendar cita y seleccionar un horario y médico (P5.1.1 Path: Menú Paciente - Agendar cita) de los indicados en las opciones con disponibilidad </t>
   </si>
   <si>
     <t>Clic en el boton ENVIAR</t>
   </si>
   <si>
-    <t>El sistema confirma el agendamiento exitoso de la cita 'Cita agendada exitosamente el día x a la hora y con el médico z' y vuelve a mi menú.</t>
+    <t>El sistema confirma el agendamiento exitoso de la cita 'Cita agendada exitosamente el día x a la hora y con el médico z'  (P5.1.1 Path: Menú Paciente - Agendar cita) y vuelve a mi menú.</t>
   </si>
   <si>
     <t>Agendamiento rápido</t>
   </si>
   <si>
-    <t>En caso de entrar a agendar cita y seleccionar el horario disponible más proximo</t>
+    <t>Dado que estando en el panel de Paciente (P5 Path: Menú Paciente), en caso de entrar a agendar cita y seleccionar el horario disponible más proximo  (P5.1.2 Path: Menú Paciente - Agendar cita)</t>
   </si>
   <si>
     <t>Clic en el botón ENVIAR</t>
   </si>
   <si>
+    <t>El sistema confirma el agendamiento exitoso de la cita 'Cita agendada exitosamente el día x a la hora y con el médico z'  (P5.1.2 Path: Menú Paciente - Agendar cita) y vuelve a mi menú.</t>
+  </si>
+  <si>
     <t>Agendamiento fallido por solapamiento</t>
   </si>
   <si>
-    <t>En caso de entrar a agendar cita y seleccionar un horario con un medico en el cual ya tenía una cita agendada con otro medico</t>
+    <t>Dado que estando en el panel de Paciente (P5 Path: Menú Paciente), en caso de entrar a agendar cita y seleccionar un horario con un medico en el cual ya tenía una cita agendada con otro medico  (P5.1.3 Path: Menú Paciente - Agendar cita)</t>
   </si>
   <si>
-    <t>El sistema muestra el mensaje:'Usted ya tiene agenda una cita en este horario con otro médico'.</t>
+    <t>El sistema muestra el mensaje:'Usted ya tiene agenda una cita en este horario'  (P5.1.3.1 Path: Menú Paciente - Agendar cita).</t>
   </si>
   <si>
-    <t>Agendamiento fallido por medico no disponible</t>
+    <t>Agendamiento fallido por medico inactivo</t>
   </si>
   <si>
-    <t>En caso de entrar a agendar cita e intentar seleccionar un medico sin disponibilidad</t>
+    <t>Dado que estando en el panel de Paciente (P5 Path: Menú Paciente), en caso de entrar a agendar cita e intentar seleccionar un medico sin disponibilidad  (P5.1.4 Path: Menú Paciente - Agendar cita)</t>
   </si>
   <si>
     <t>Opciones inhabilitadas</t>
   </si>
   <si>
-    <t>El sistema inhabilita u oculta las opciones de agendamiento</t>
+    <t>El sistema inhabilita u oculta las opciones de agendamiento  (P5.1.4.1 Path: Menú Paciente - Agendar cita)</t>
   </si>
   <si>
     <t>Agendamiento fallido por pasar fecha límite</t>
   </si>
   <si>
-    <t>En caso de entrar a agendar cita en un tiempo más allá del límite establecido por el administrador</t>
+    <t>Dado que estando en el panel de Paciente (P5 Path: Menú Paciente), en caso de entrar a agendar cita en un tiempo más allá del límite establecido por el administrador (P5.1.5 Path: Menú Paciente - Agendar cita)</t>
   </si>
   <si>
     <t>Clic en FILTRAR</t>
   </si>
   <si>
-    <t>El sistema muestra mensaje 'No puede agendar una cita más allá de 3 meses'</t>
+    <t>El sistema muestra mensaje 'No puede agendar una cita más allá de x tiempo' (P5.1.5.1 Path: Menú Paciente - Agendar cita)</t>
   </si>
   <si>
     <t>Agendamiento fallido por simultaneidad</t>
   </si>
   <si>
-    <t>En caso de que dos usuarios intenten agendar su cita en el mismo horario simultáneamente</t>
+    <t>Dado que estando en el panel de Paciente (P5 Path: Menú Paciente), en caso de que dos usuarios intenten agendar su cita en el mismo horario simultáneamente (P5.1.6.1/P5.1.6.2 Path: Menú Paciente - Agendar cita)</t>
   </si>
   <si>
     <t>Al ENVIAR</t>
   </si>
   <si>
-    <t>El sistema confirma agendamiento a uno y al otro muestra 'Horario no disponible para agendamiento'</t>
+    <t>El sistema confirma agendamiento a uno (P5.1.6.1.1 Path: Menú Paciente - Agendar cita) y al otro muestra 'Horario no disponible para agendamiento'  (P5.1.6.2.1 Path: Menú Paciente - Agendar cita)</t>
   </si>
   <si>
     <t>HU-1.2</t>
@@ -220,6 +217,12 @@
     <t>Desarrollo ágil: Historias de Usuario y criterios de aceptación de HE-02</t>
   </si>
   <si>
+    <t>Vista navegador</t>
+  </si>
+  <si>
+    <t>Vista Movil</t>
+  </si>
+  <si>
     <t>HE-02</t>
   </si>
   <si>
@@ -265,7 +268,16 @@
     <t>El sistema muestra el mensaje:'El paciente ya tiene agenda una cita en este horario con otro médico'.</t>
   </si>
   <si>
+    <t>En caso de que dos usuarios intenten agendar su cita en el mismo horario simultáneamente</t>
+  </si>
+  <si>
+    <t>El sistema confirma agendamiento a uno y al otro muestra 'Horario no disponible para agendamiento'</t>
+  </si>
+  <si>
     <t>En caso de haber ingresado a agendar cita y seleccionar un horario más allá del tiempo límite establecido por el administrador</t>
+  </si>
+  <si>
+    <t>El sistema muestra mensaje 'No puede agendar una cita más allá de 3 meses'</t>
   </si>
   <si>
     <t>Agendamiento fallido por datos incompatibles</t>
@@ -295,16 +307,49 @@
     <t>Para poder brindarle atención medica y asignarle un médico y horario disponible</t>
   </si>
   <si>
-    <t>En caso de haber ingresado a agendar cita y seleccionar un horario y médico de los indicados en las opciones con disponibilidad, ingresar la CC del paciente</t>
+    <t>Dado que estando en el panel de Agendador(P6 Path: Menú Agendador), en caso de haber ingresado a agendar cita y seleccionar un horario y médico de los indicados en las opciones con disponibilidad, ingresar la CC del paciente (P6.1.1 Path: Menú Agendador- Agendar cita)</t>
   </si>
   <si>
-    <t>En caso de haber ingresado a agendar cita y seleccionar un horario y medico de los indicados en las opciones con disponibilidad, ingresar los datos obligatorios del paciente en el formulario (marcados con asterisco *)</t>
+    <t>El sistema confirma el agendamiento de la cita para el paciente registrado a través de un mensaje (P6.1.2 Path: Menú Agendador- Agendar cita).</t>
   </si>
   <si>
-    <t>En caso de haber ingresado a agendar cita y seleccionar un horario y medico de los indicados en las opciones con disponibilidad</t>
+    <t>Dado que estando en el panel de Agendador(P6 Path: Menú Agendador), en caso de haber ingresado a agendar cita y seleccionar un horario y medico de los indicados en las opciones con disponibilidad, ingresar los datos obligatorios del paciente en el formulario (marcados con asterisco *) (P6.1.3 Path: Menú Agendador- Agendar cita)</t>
   </si>
   <si>
-    <t>El sistema muestra el mensaje:'El paciente ya tiene agendada una cita en este horario con otro médico'.</t>
+    <t>El sistema confirma el agendamiento de la cita para el paciente registrado por formulario a través de un mensaje. Este paciente no se registrará en el sistema, únicamente agenda su cita. (P6.1.4 Path: Menú Agendador- Agendar cita)</t>
+  </si>
+  <si>
+    <t>Dado que estando en el panel de Agendador(P6 Path: Menú Agendador), en caso de haber ingresado a agendar cita y seleccionar un horario y medico de los indicados en las opciones con disponibilidad (P6.1.5 Path: Menú Agendador- Agendar cita)</t>
+  </si>
+  <si>
+    <t>El sistema muestra el mensaje:'El paciente ya tiene agendada una cita en este horario'. (P6.1.6 Path: Menú Agendador- Agendar cita)</t>
+  </si>
+  <si>
+    <t>Dado que estando en el panel de Agendador(P6 Path: Menú Agendador), en caso de que dos usuarios intenten agendar su cita en el mismo horario simultáneamente (P6.1.7 Path: Menú Agendador- Agendar cita)</t>
+  </si>
+  <si>
+    <t>El sistema confirma agendamiento a uno y al otro muestra 'Horario no disponible para agendamiento' (P6.1.8 Path: Menú Agendador- Agendar cita)</t>
+  </si>
+  <si>
+    <t>Dado que estando en el panel de Agendador(P6 Path: Menú Agendador), en caso de haber ingresado a agendar cita y seleccionar un horario más allá del tiempo límite establecido por el administrador (P6.1.9 Path: Menú Agendador- Agendar cita)</t>
+  </si>
+  <si>
+    <t>El sistema muestra mensaje 'No puede agendar una cita más allá de 3 meses' (P6.1.10 Path: Menú Agendador- Agendar cita)</t>
+  </si>
+  <si>
+    <t>Agendamiento fallido por medico no disponible</t>
+  </si>
+  <si>
+    <t>Dado que estando en el panel de Agendador(P6 Path: Menú Agendador), en caso de entrar a agendar cita e intentar seleccionar un medico sin disponibilidad</t>
+  </si>
+  <si>
+    <t>El sistema inhabilita u oculta las opciones de agendamiento</t>
+  </si>
+  <si>
+    <t>Dado que estando en el panel de Agendador(P6 Path: Menú Agendador), en caso de haber ingresado a agendar cita y seleccionar un horario de los indicados en las opciones con disponibilidad, ingresar los datos obligatorios del paciente en el formulario (marcados con asterisco *) pero con datos incompatibles a los esperados</t>
+  </si>
+  <si>
+    <t>Dado que estando en el panel de Agendador(P6 Path: Menú Agendador), en caso de haber ingresado a agendar cita y seleccionar un horario de los indicados en las opciones con disponibilidad, ingresar los datos del paciente en el formulario pero dejando campos obligatorios vacíos</t>
   </si>
   <si>
     <t>HU-2.3</t>
@@ -359,6 +404,9 @@
   </si>
   <si>
     <t>En caso de haber ingresado a reagendar cita en la opción indicada al seleccionar el paciente en el listado de citas y seleccionar un horario y medico de los indicados en las opciones con disponibilidad</t>
+  </si>
+  <si>
+    <t>El sistema muestra el mensaje:'El paciente ya tiene agendada una cita en este horario con otro médico'.</t>
   </si>
   <si>
     <t>Reagendamiento fallido por simultaneidad</t>
@@ -457,28 +505,31 @@
     <t>Listado exitoso</t>
   </si>
   <si>
-    <t>En caso de haber ingresado al listado/historial de citas (P xxxxx) y haber filtrado por medico y por fecha</t>
+    <t>Dado que estando en el panel de Agendador(P6 Path: Menú Agendador), en caso de haber ingresado al listado/historial de citas (P6.2. Path: Menú Agendador- Historia de citas) y haber filtrado por medico y por fecha</t>
   </si>
   <si>
     <t>Al LISTAR</t>
   </si>
   <si>
-    <t>El sistema muestra en una tabla con columnas de fecha,  hora, paciente, médico y descripción (P xxxx)</t>
+    <t>El sistema muestra en una tabla con columnas de fecha,  hora, paciente, médico y descripción (P6.2.1 Path: Menú Agendador- Historial de citas)</t>
   </si>
   <si>
     <t>Listado exitoso vacío</t>
   </si>
   <si>
-    <t>El sistema muestra en un mensaje 'No hay citas registradas para el médico y fecha seleccionados' (P xxxx)</t>
+    <t>Dado que estando en el panel de Agendador(P6 Path: Menú Agendador), en caso de haber ingresado al listado/historial de citas (P6.2 Path: Menú Agendador- Historial de citas) y haber filtrado por medico y por fecha</t>
+  </si>
+  <si>
+    <t>El sistema muestra en un mensaje 'No hay citas registradas para el médico y fecha seleccionados' (P6.2.2 Path: Menú Agendador- Historial de citas)</t>
   </si>
   <si>
     <t>Listado fallido por rango de fecha</t>
   </si>
   <si>
-    <t>En caso de haber ingresado al listado/historial de citas (P xxxxx) y haber filtrado por medico y por fecha pero fuera del límite de tiempo</t>
+    <t>Dado que estando en el panel de Agendador(P6 Path: Menú Agendador), en caso de haber ingresado al listado/historial de citas (P6.2 Path: Menú Agendador- Historia de citas) y haber filtrado por medico y por fecha pero fuera del límite de tiempo</t>
   </si>
   <si>
-    <t>El sistema muestra un mensaje que dice 'Excedió el rango de tiempo, no encontrará citas' (P xxxxx)</t>
+    <t>El sistema muestra un mensaje que dice 'Excedió el rango de tiempo, no encontrará citas' (P6.2.3 Path: Menú Agendador- Historial de citas)</t>
   </si>
   <si>
     <t>Desarrollo ágil: Historias de Usuario y criterios de aceptación de HE-03</t>
@@ -754,6 +805,9 @@
     <t>El sistema cierra la sesión y guarda el token de sesión</t>
   </si>
   <si>
+    <t>Desarrollo ágil: Historias de Usuario y criterios de aceptación de HE-05</t>
+  </si>
+  <si>
     <t>HE-05</t>
   </si>
   <si>
@@ -781,7 +835,7 @@
         <color rgb="FF000000"/>
         <sz val="11.0"/>
       </rPr>
-      <t xml:space="preserve">El sistema confirma la configuración a través de un mensaje (P xxxxx) 'Se han habilitado citas hasta dentro de </t>
+      <t xml:space="preserve">El sistema confirma la configuración a través de un mensaje (P3.6.1.2.1 path: Inicio de Sesión-Menú Administrador-Configuración Horarios-Configuración Semanas) 'Se han habilitado citas hasta dentro de </t>
     </r>
     <r>
       <rPr>
@@ -808,7 +862,7 @@
     <t>Dado que ingresé a la aplicación, inicié sesión (P1 path: Inicio de Sesión) y en el panel de administrador (P3 path: Inicio de Sesión-Menú Administrador) entré a la opción de configuración de horarios(P3.6 path: Inicio de Sesión-Menú Administrador-Configuración Horarios), seleccioné la opción Configurar intervalo para agendamiento (P3.6.1.1 path: Inicio de Sesión-Menú Administrador-Configuración Horarios-Configuración Semanas) e ingresé caracteres especiales, letras, número decimal o dejé vacío</t>
   </si>
   <si>
-    <t>El sistema resalta que la configuración no fue exitosa a través de un mensaje (P xxxxx) 'Debe ingresar un número entero'</t>
+    <t>El sistema resalta que la configuración no fue exitosa a través de un mensaje (P3.6.1.3.1 path: Inicio de Sesión-Menú Administrador-Configuración Horarios-Configuración Semanas) 'Debe ingresar un número entero'</t>
   </si>
   <si>
     <t>HU-5.2</t>
@@ -826,7 +880,7 @@
     <t>Dado que ingresé a la aplicación, inicié sesión (P1 path: Inicio de Sesión) y en el panel de administrador (P3 path: Inicio de Sesión-Menú Administrador) entré a la opción de configuración de horarios(P3.6 path: Inicio de Sesión-Menú Administrador-Configuración Horarios), seleccioné la opción Configurar horarios de atención (P3.6.2.1 path: Inicio de Sesión-Menú Administrador-Configuración Horarios-Configurar Franjas Atención), seleccioné el médico y luego los días y franjas horarios a asignarle correctamente</t>
   </si>
   <si>
-    <t>El sistema informa que 'La configuración de horarios ha sido exitosa' a través de un mensaje (P xxxxx)</t>
+    <t>El sistema informa que 'La configuración de horarios ha sido exitosa' a través de un mensaje (P3.6.2.2.1 path: Inicio de Sesión-Menú Administrador-Configuración Horarios-Configuración Semanas)</t>
   </si>
   <si>
     <t>HU-5.3</t>
@@ -850,7 +904,7 @@
         <color rgb="FF000000"/>
         <sz val="11.0"/>
       </rPr>
-      <t xml:space="preserve">El sistema confirma la configuración a través de un mensaje (P xxxxxx) 'Se ha establecido el intervalo entre citas a </t>
+      <t xml:space="preserve">El sistema confirma la configuración a través de un mensaje (P3.6.3.2.1 path: Inicio de Sesión-Menú Administrador-Configuración Horarios-Configuración Semanas) 'Se ha establecido el intervalo entre citas a </t>
     </r>
     <r>
       <rPr>
@@ -877,7 +931,7 @@
     <t>Dado que ingresé a la aplicación, inicié sesión (P1 path: Inicio de Sesión) y en el panel de administrador (P3 path: Inicio de Sesión-Menú Administrador) entré a la opción de configuración de horarios(P3.6 path: Inicio de Sesión-Menú Administrador-Configuración Horarios), seleccioné la opción Configurar intervalos entre citas (P3.6.3.1 path: Inicio de Sesión-Menú Administrador-Configuración Horarios-Configuración Intervalos), e ingresé el número de minutos fuera del tiempo límite</t>
   </si>
   <si>
-    <t xml:space="preserve">El sistema lanza un mensaje 'Intervalo fuera de tiempo' (P ****) </t>
+    <t>El sistema lanza un mensaje 'Intervalo fuera de tiempo'</t>
   </si>
 </sst>
 </file>
@@ -958,7 +1012,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="36">
+  <borders count="29">
     <border/>
     <border>
       <left/>
@@ -1011,6 +1065,11 @@
       </bottom>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -1028,43 +1087,12 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
     </border>
     <border>
       <left style="thin">
@@ -1084,25 +1112,9 @@
       <bottom/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <left/>
+      <right/>
+      <bottom/>
     </border>
     <border>
       <left/>
@@ -1201,16 +1213,11 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <bottom/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="65">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1229,129 +1236,129 @@
     </xf>
     <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="8" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="9" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="10" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="11" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="12" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="10" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="10" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="9" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="9" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="9" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf borderId="11" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="12" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="11" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="9" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="9" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="13" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="14" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="15" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="16" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="17" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="18" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="9" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="19" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="20" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="21" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="22" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="23" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="13" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="14" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="15" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="24" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="9" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="25" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="9" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="10" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="16" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="15" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="10" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="26" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="10" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="17" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="18" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="19" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf borderId="27" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="20" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="21" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="22" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="23" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="24" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="25" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="26" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="27" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="28" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="29" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="30" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="31" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="32" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="12" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="33" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="15" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="15" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="15" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="34" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="35" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="12" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="28" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="10" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="29" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="23" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1374,123 +1381,11 @@
     <xdr:ext cx="9525" cy="9525"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="Imagen"/>
+        <xdr:cNvPr id="0" name="image1.png" title="Imagen"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="666750" cy="314325"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="457200" cy="561975"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.png"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="390525" cy="190500"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.png"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="133350" cy="190500"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.png"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1519,7 +1414,7 @@
     <xdr:ext cx="9525" cy="9525"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="Imagen"/>
+        <xdr:cNvPr id="0" name="image1.png" title="Imagen"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1552,7 +1447,7 @@
     <xdr:ext cx="9525" cy="9525"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="Imagen"/>
+        <xdr:cNvPr id="0" name="image1.png" title="Imagen"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1585,7 +1480,7 @@
     <xdr:ext cx="9525" cy="9525"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="Imagen"/>
+        <xdr:cNvPr id="0" name="image1.png" title="Imagen"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1618,7 +1513,7 @@
     <xdr:ext cx="9525" cy="9525"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="Imagen"/>
+        <xdr:cNvPr id="0" name="image1.png" title="Imagen"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1960,514 +1855,466 @@
       <c r="J4" s="8"/>
       <c r="K4" s="9"/>
       <c r="L4" s="1"/>
-      <c r="M4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
-      <c r="T4" s="1"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="10"/>
+      <c r="T4" s="10"/>
       <c r="U4" s="1"/>
-      <c r="V4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W4" s="1"/>
-      <c r="X4" s="1"/>
+      <c r="V4" s="10"/>
+      <c r="W4" s="10"/>
+      <c r="X4" s="10"/>
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
       <c r="AA4" s="1"/>
     </row>
     <row r="5" ht="44.25" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="E5" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="F5" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="G5" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="H5" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="I5" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="J5" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="K5" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="L5" s="1"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="12"/>
-      <c r="O5" s="12"/>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12"/>
-      <c r="S5" s="12"/>
-      <c r="T5" s="13"/>
-      <c r="U5" s="1"/>
-      <c r="V5" s="11"/>
-      <c r="W5" s="12"/>
-      <c r="X5" s="13"/>
-      <c r="Y5" s="1"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="13"/>
+      <c r="U5" s="14"/>
+      <c r="V5" s="13"/>
+      <c r="Y5" s="15"/>
       <c r="Z5" s="1"/>
       <c r="AA5" s="1"/>
     </row>
     <row r="6">
       <c r="A6" s="1"/>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="E6" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="F6" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="G6" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="H6" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="I6" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="16">
-        <v>1.0</v>
-      </c>
-      <c r="H6" s="17" t="s">
+      <c r="J6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="I6" s="17" t="s">
+      <c r="K6" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="J6" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="K6" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="L6" s="19"/>
-      <c r="M6" s="20"/>
-      <c r="T6" s="21"/>
-      <c r="U6" s="1"/>
-      <c r="V6" s="20"/>
-      <c r="X6" s="21"/>
-      <c r="Y6" s="1"/>
+      <c r="L6" s="23"/>
+      <c r="U6" s="14"/>
+      <c r="Y6" s="15"/>
       <c r="Z6" s="1"/>
       <c r="AA6" s="1"/>
     </row>
     <row r="7">
       <c r="A7" s="1"/>
-      <c r="B7" s="22"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="16">
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="18">
         <v>2.0</v>
       </c>
-      <c r="H7" s="23" t="s">
+      <c r="H7" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="17" t="s">
+      <c r="K7" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="J7" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="K7" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="L7" s="19"/>
-      <c r="M7" s="20"/>
-      <c r="T7" s="21"/>
-      <c r="U7" s="1"/>
-      <c r="V7" s="20"/>
-      <c r="X7" s="21"/>
-      <c r="Y7" s="1"/>
+      <c r="L7" s="23"/>
+      <c r="U7" s="14"/>
+      <c r="Y7" s="15"/>
       <c r="Z7" s="1"/>
       <c r="AA7" s="1"/>
     </row>
     <row r="8">
       <c r="A8" s="1"/>
-      <c r="B8" s="22"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="16">
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="18">
         <v>3.0</v>
       </c>
-      <c r="H8" s="17" t="s">
+      <c r="H8" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="I8" s="17" t="s">
+      <c r="J8" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="J8" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="K8" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="L8" s="1"/>
-      <c r="M8" s="20"/>
-      <c r="T8" s="21"/>
-      <c r="U8" s="1"/>
-      <c r="V8" s="20"/>
-      <c r="X8" s="21"/>
-      <c r="Y8" s="1"/>
+      <c r="L8" s="12"/>
+      <c r="U8" s="14"/>
+      <c r="Y8" s="15"/>
       <c r="Z8" s="1"/>
       <c r="AA8" s="1"/>
     </row>
     <row r="9">
       <c r="A9" s="1"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="16">
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="18">
         <v>4.0</v>
       </c>
-      <c r="H9" s="24" t="s">
+      <c r="H9" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="I9" s="17" t="s">
+      <c r="J9" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="J9" s="18" t="s">
+      <c r="K9" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="K9" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="L9" s="1"/>
-      <c r="M9" s="20"/>
-      <c r="T9" s="21"/>
-      <c r="U9" s="1"/>
-      <c r="V9" s="20"/>
-      <c r="X9" s="21"/>
-      <c r="Y9" s="1"/>
+      <c r="L9" s="12"/>
+      <c r="U9" s="14"/>
+      <c r="Y9" s="15"/>
       <c r="Z9" s="1"/>
       <c r="AA9" s="1"/>
     </row>
     <row r="10">
       <c r="A10" s="1"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="16">
+      <c r="B10" s="24"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="18">
         <v>5.0</v>
       </c>
-      <c r="H10" s="26" t="s">
+      <c r="H10" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="I10" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I10" s="23" t="s">
+      <c r="J10" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="J10" s="18" t="s">
+      <c r="K10" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="K10" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="L10" s="1"/>
-      <c r="M10" s="20"/>
-      <c r="T10" s="21"/>
-      <c r="U10" s="1"/>
-      <c r="V10" s="20"/>
-      <c r="X10" s="21"/>
-      <c r="Y10" s="1"/>
+      <c r="L10" s="12"/>
+      <c r="U10" s="14"/>
+      <c r="Y10" s="15"/>
       <c r="Z10" s="1"/>
       <c r="AA10" s="1"/>
     </row>
     <row r="11">
       <c r="A11" s="1"/>
-      <c r="B11" s="22"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="16">
+      <c r="B11" s="24"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="18">
         <v>6.0</v>
       </c>
-      <c r="H11" s="26" t="s">
+      <c r="H11" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I11" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="I11" s="17" t="s">
+      <c r="J11" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="J11" s="18" t="s">
+      <c r="K11" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="K11" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="L11" s="1"/>
-      <c r="M11" s="20"/>
-      <c r="T11" s="21"/>
-      <c r="U11" s="1"/>
-      <c r="V11" s="20"/>
-      <c r="X11" s="21"/>
-      <c r="Y11" s="1"/>
+      <c r="L11" s="12"/>
+      <c r="U11" s="14"/>
+      <c r="Y11" s="15"/>
       <c r="Z11" s="1"/>
       <c r="AA11" s="1"/>
     </row>
     <row r="12">
       <c r="A12" s="1"/>
-      <c r="B12" s="22"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="28"/>
-      <c r="J12" s="28"/>
-      <c r="K12" s="28"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="30"/>
-      <c r="N12" s="31"/>
-      <c r="O12" s="31"/>
-      <c r="P12" s="31"/>
-      <c r="Q12" s="31"/>
-      <c r="R12" s="31"/>
-      <c r="S12" s="31"/>
-      <c r="T12" s="32"/>
-      <c r="U12" s="1"/>
-      <c r="V12" s="30"/>
-      <c r="W12" s="31"/>
-      <c r="X12" s="32"/>
-      <c r="Y12" s="1"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="29"/>
+      <c r="K12" s="29"/>
+      <c r="L12" s="12"/>
+      <c r="U12" s="14"/>
+      <c r="Y12" s="15"/>
       <c r="Z12" s="1"/>
       <c r="AA12" s="1"/>
     </row>
     <row r="13">
       <c r="A13" s="1"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="15" t="s">
+      <c r="B13" s="24"/>
+      <c r="C13" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="15" t="s">
+      <c r="F13" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F13" s="15" t="s">
+      <c r="G13" s="31">
+        <v>1.0</v>
+      </c>
+      <c r="H13" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="G13" s="33">
-        <v>1.0</v>
-      </c>
-      <c r="H13" s="34" t="s">
+      <c r="I13" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="I13" s="17" t="s">
+      <c r="J13" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="J13" s="18" t="s">
+      <c r="K13" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="K13" s="18" t="s">
-        <v>48</v>
-      </c>
       <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1"/>
-      <c r="Q13" s="1"/>
-      <c r="R13" s="1"/>
-      <c r="S13" s="1"/>
-      <c r="T13" s="1"/>
+      <c r="M13" s="33"/>
+      <c r="N13" s="33"/>
+      <c r="O13" s="33"/>
+      <c r="P13" s="33"/>
+      <c r="Q13" s="33"/>
+      <c r="R13" s="33"/>
+      <c r="S13" s="33"/>
+      <c r="T13" s="33"/>
       <c r="U13" s="1"/>
-      <c r="V13" s="1"/>
-      <c r="W13" s="1"/>
-      <c r="X13" s="1"/>
+      <c r="V13" s="33"/>
+      <c r="W13" s="33"/>
+      <c r="X13" s="33"/>
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
       <c r="AA13" s="1"/>
     </row>
     <row r="14">
       <c r="A14" s="1"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="16">
+      <c r="B14" s="24"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="18">
         <v>2.0</v>
       </c>
-      <c r="H14" s="17" t="s">
+      <c r="H14" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="I14" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="J14" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="K14" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="I14" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="J14" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="K14" s="18" t="s">
-        <v>50</v>
-      </c>
       <c r="L14" s="1"/>
-      <c r="M14" s="35"/>
-      <c r="N14" s="36"/>
-      <c r="O14" s="36"/>
-      <c r="P14" s="36"/>
-      <c r="Q14" s="36"/>
-      <c r="R14" s="36"/>
-      <c r="S14" s="36"/>
-      <c r="T14" s="37"/>
+      <c r="M14" s="34"/>
+      <c r="N14" s="35"/>
+      <c r="O14" s="35"/>
+      <c r="P14" s="35"/>
+      <c r="Q14" s="35"/>
+      <c r="R14" s="35"/>
+      <c r="S14" s="35"/>
+      <c r="T14" s="36"/>
       <c r="U14" s="1"/>
-      <c r="V14" s="35"/>
-      <c r="W14" s="36"/>
-      <c r="X14" s="37"/>
+      <c r="V14" s="34"/>
+      <c r="W14" s="35"/>
+      <c r="X14" s="36"/>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
       <c r="AA14" s="1"/>
     </row>
     <row r="15">
       <c r="A15" s="1"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="16">
+      <c r="B15" s="24"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="18">
         <v>3.0</v>
       </c>
-      <c r="H15" s="17" t="s">
+      <c r="H15" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="I15" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="J15" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="I15" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="J15" s="18" t="s">
+      <c r="K15" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="K15" s="18" t="s">
-        <v>53</v>
-      </c>
       <c r="L15" s="1"/>
-      <c r="M15" s="38"/>
-      <c r="T15" s="39"/>
+      <c r="M15" s="37"/>
+      <c r="T15" s="38"/>
       <c r="U15" s="1"/>
-      <c r="V15" s="38"/>
-      <c r="X15" s="39"/>
+      <c r="V15" s="37"/>
+      <c r="X15" s="38"/>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
       <c r="AA15" s="1"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="1"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="28"/>
-      <c r="J16" s="28"/>
-      <c r="K16" s="28"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="29"/>
+      <c r="K16" s="29"/>
       <c r="L16" s="1"/>
-      <c r="M16" s="38"/>
-      <c r="T16" s="39"/>
+      <c r="M16" s="37"/>
+      <c r="T16" s="38"/>
       <c r="U16" s="1"/>
-      <c r="V16" s="38"/>
-      <c r="X16" s="39"/>
+      <c r="V16" s="37"/>
+      <c r="X16" s="38"/>
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
       <c r="AA16" s="1"/>
     </row>
     <row r="17">
       <c r="A17" s="1"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="15" t="s">
+      <c r="B17" s="24"/>
+      <c r="C17" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="15" t="s">
+      <c r="F17" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="F17" s="15" t="s">
+      <c r="G17" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="H17" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="G17" s="16">
-        <v>1.0</v>
-      </c>
-      <c r="H17" s="34" t="s">
+      <c r="I17" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="I17" s="34" t="s">
+      <c r="J17" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="J17" s="34" t="s">
+      <c r="K17" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="K17" s="34" t="s">
-        <v>60</v>
-      </c>
       <c r="L17" s="1"/>
-      <c r="M17" s="38"/>
-      <c r="T17" s="39"/>
+      <c r="M17" s="37"/>
+      <c r="T17" s="38"/>
       <c r="U17" s="1"/>
-      <c r="V17" s="38"/>
-      <c r="X17" s="39"/>
+      <c r="V17" s="37"/>
+      <c r="X17" s="38"/>
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
       <c r="AA17" s="1"/>
     </row>
     <row r="18">
       <c r="A18" s="1"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="16">
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="18">
         <v>2.0</v>
       </c>
-      <c r="H18" s="17" t="s">
+      <c r="H18" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="I18" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="J18" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="I18" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="J18" s="17" t="s">
+      <c r="K18" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="K18" s="17" t="s">
-        <v>63</v>
-      </c>
       <c r="L18" s="1"/>
-      <c r="M18" s="38"/>
-      <c r="T18" s="39"/>
+      <c r="M18" s="37"/>
+      <c r="T18" s="38"/>
       <c r="U18" s="1"/>
-      <c r="V18" s="38"/>
-      <c r="X18" s="39"/>
+      <c r="V18" s="37"/>
+      <c r="X18" s="38"/>
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
       <c r="AA18" s="1"/>
@@ -2479,20 +2326,20 @@
       <c r="D19" s="40"/>
       <c r="E19" s="40"/>
       <c r="F19" s="40"/>
-      <c r="G19" s="16">
+      <c r="G19" s="18">
         <v>3.0</v>
       </c>
-      <c r="H19" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="I19" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="J19" s="18" t="s">
+      <c r="H19" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="I19" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="J19" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="K19" s="21" t="s">
         <v>52</v>
-      </c>
-      <c r="K19" s="18" t="s">
-        <v>53</v>
       </c>
       <c r="L19" s="1"/>
       <c r="M19" s="41"/>
@@ -9101,7 +8948,7 @@
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="44" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
@@ -9204,7 +9051,7 @@
       <c r="K4" s="9"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1" t="s">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
@@ -9215,7 +9062,7 @@
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
       <c r="V4" s="1" t="s">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
@@ -9225,35 +9072,35 @@
     </row>
     <row r="5" ht="44.25" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="E5" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="F5" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="G5" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="H5" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="I5" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="J5" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="K5" s="11" t="s">
         <v>12</v>
-      </c>
-      <c r="J5" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>14</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -9275,36 +9122,36 @@
     <row r="6">
       <c r="A6" s="1"/>
       <c r="B6" s="45" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="C6" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="D6" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="E6" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="G6" s="16">
+      <c r="F6" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="G6" s="18">
         <v>1.0</v>
       </c>
-      <c r="H6" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="I6" s="17" t="s">
+      <c r="H6" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="J6" s="18" t="s">
+      <c r="I6" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="K6" s="18" t="s">
+      <c r="J6" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="L6" s="19"/>
+      <c r="K6" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="L6" s="46"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
@@ -9323,25 +9170,25 @@
     </row>
     <row r="7">
       <c r="A7" s="1"/>
-      <c r="B7" s="46"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="16">
+      <c r="B7" s="47"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="18">
         <v>2.0</v>
       </c>
-      <c r="H7" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="I7" s="17" t="s">
+      <c r="H7" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="J7" s="18" t="s">
+      <c r="I7" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="K7" s="18" t="s">
+      <c r="J7" s="21" t="s">
         <v>78</v>
+      </c>
+      <c r="K7" s="21" t="s">
+        <v>79</v>
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
@@ -9362,25 +9209,25 @@
     </row>
     <row r="8">
       <c r="A8" s="1"/>
-      <c r="B8" s="46"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="16">
+      <c r="B8" s="47"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="18">
         <v>3.0</v>
       </c>
-      <c r="H8" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="I8" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="J8" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="K8" s="18" t="s">
+      <c r="H8" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" s="19" t="s">
         <v>80</v>
+      </c>
+      <c r="J8" s="48" t="s">
+        <v>78</v>
+      </c>
+      <c r="K8" s="21" t="s">
+        <v>81</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -9401,25 +9248,25 @@
     </row>
     <row r="9">
       <c r="A9" s="1"/>
-      <c r="B9" s="46"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="16">
+      <c r="B9" s="47"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="18">
         <v>4.0</v>
       </c>
-      <c r="H9" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="I9" s="17" t="s">
+      <c r="H9" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I9" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="J9" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="J9" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="K9" s="18" t="s">
-        <v>41</v>
+      <c r="K9" s="21" t="s">
+        <v>83</v>
       </c>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -9440,25 +9287,25 @@
     </row>
     <row r="10">
       <c r="A10" s="1"/>
-      <c r="B10" s="46"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="16">
+      <c r="B10" s="47"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="18">
         <v>5.0</v>
       </c>
-      <c r="H10" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="I10" s="23" t="s">
-        <v>81</v>
-      </c>
-      <c r="J10" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="K10" s="18" t="s">
-        <v>37</v>
+      <c r="H10" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="I10" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="J10" s="48" t="s">
+        <v>78</v>
+      </c>
+      <c r="K10" s="21" t="s">
+        <v>85</v>
       </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -9479,25 +9326,25 @@
     </row>
     <row r="11">
       <c r="A11" s="1"/>
-      <c r="B11" s="46"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="47">
+      <c r="B11" s="47"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="49">
         <v>6.0</v>
       </c>
-      <c r="H11" s="48" t="s">
-        <v>82</v>
-      </c>
-      <c r="I11" s="23" t="s">
-        <v>83</v>
-      </c>
-      <c r="J11" s="48" t="s">
-        <v>40</v>
-      </c>
-      <c r="K11" s="49" t="s">
-        <v>84</v>
+      <c r="H11" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="I11" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="J11" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>88</v>
       </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -9518,25 +9365,25 @@
     </row>
     <row r="12">
       <c r="A12" s="1"/>
-      <c r="B12" s="46"/>
+      <c r="B12" s="47"/>
       <c r="C12" s="40"/>
       <c r="D12" s="40"/>
       <c r="E12" s="40"/>
       <c r="F12" s="40"/>
-      <c r="G12" s="47">
+      <c r="G12" s="49">
         <v>7.0</v>
       </c>
-      <c r="H12" s="48" t="s">
-        <v>85</v>
-      </c>
-      <c r="I12" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="J12" s="48" t="s">
-        <v>40</v>
-      </c>
-      <c r="K12" s="49" t="s">
-        <v>87</v>
+      <c r="H12" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="I12" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="J12" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>91</v>
       </c>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
@@ -9557,16 +9404,16 @@
     </row>
     <row r="13">
       <c r="A13" s="1"/>
-      <c r="B13" s="46"/>
+      <c r="B13" s="47"/>
       <c r="C13" s="50"/>
       <c r="D13" s="50"/>
       <c r="E13" s="50"/>
       <c r="F13" s="50"/>
-      <c r="G13" s="29"/>
+      <c r="G13" s="30"/>
       <c r="H13" s="51"/>
-      <c r="I13" s="28"/>
-      <c r="J13" s="28"/>
-      <c r="K13" s="28"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="29"/>
+      <c r="K13" s="29"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
@@ -9586,33 +9433,33 @@
     </row>
     <row r="14">
       <c r="A14" s="1"/>
-      <c r="B14" s="46"/>
-      <c r="C14" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="G14" s="16">
+      <c r="B14" s="47"/>
+      <c r="C14" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="G14" s="18">
         <v>1.0</v>
       </c>
-      <c r="H14" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="I14" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="J14" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="K14" s="18" t="s">
+      <c r="H14" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I14" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="J14" s="21" t="s">
         <v>74</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>96</v>
       </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -9633,25 +9480,25 @@
     </row>
     <row r="15">
       <c r="A15" s="1"/>
-      <c r="B15" s="46"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="16">
+      <c r="B15" s="47"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="18">
         <v>2.0</v>
       </c>
-      <c r="H15" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="I15" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="J15" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="K15" s="18" t="s">
+      <c r="H15" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="I15" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="J15" s="21" t="s">
         <v>78</v>
+      </c>
+      <c r="K15" s="22" t="s">
+        <v>98</v>
       </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -9672,25 +9519,25 @@
     </row>
     <row r="16">
       <c r="A16" s="1"/>
-      <c r="B16" s="46"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="16">
+      <c r="B16" s="47"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="18">
         <v>3.0</v>
       </c>
-      <c r="H16" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="I16" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="J16" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="K16" s="18" t="s">
-        <v>94</v>
+      <c r="H16" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="J16" s="48" t="s">
+        <v>78</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>100</v>
       </c>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -9711,25 +9558,25 @@
     </row>
     <row r="17">
       <c r="A17" s="1"/>
-      <c r="B17" s="46"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="16">
+      <c r="B17" s="47"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="18">
         <v>4.0</v>
       </c>
-      <c r="H17" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="I17" s="17" t="s">
+      <c r="H17" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I17" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="J17" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="J17" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="K17" s="18" t="s">
-        <v>41</v>
+      <c r="K17" s="22" t="s">
+        <v>102</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -9750,25 +9597,25 @@
     </row>
     <row r="18">
       <c r="A18" s="1"/>
-      <c r="B18" s="46"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="16">
+      <c r="B18" s="47"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="18">
         <v>5.0</v>
       </c>
-      <c r="H18" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="I18" s="23" t="s">
-        <v>81</v>
-      </c>
-      <c r="J18" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="K18" s="18" t="s">
-        <v>37</v>
+      <c r="H18" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="I18" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="J18" s="48" t="s">
+        <v>78</v>
+      </c>
+      <c r="K18" s="22" t="s">
+        <v>104</v>
       </c>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -9789,25 +9636,25 @@
     </row>
     <row r="19">
       <c r="A19" s="1"/>
-      <c r="B19" s="46"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="16">
+      <c r="B19" s="47"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="18">
         <v>6.0</v>
       </c>
-      <c r="H19" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="I19" s="17" t="s">
+      <c r="H19" s="48" t="s">
+        <v>105</v>
+      </c>
+      <c r="I19" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="J19" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="J19" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="K19" s="18" t="s">
-        <v>33</v>
+      <c r="K19" s="21" t="s">
+        <v>107</v>
       </c>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -9828,25 +9675,25 @@
     </row>
     <row r="20">
       <c r="A20" s="1"/>
-      <c r="B20" s="46"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="47">
+      <c r="B20" s="47"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="49">
         <v>7.0</v>
       </c>
-      <c r="H20" s="48" t="s">
-        <v>82</v>
-      </c>
-      <c r="I20" s="23" t="s">
-        <v>83</v>
-      </c>
-      <c r="J20" s="48" t="s">
-        <v>40</v>
-      </c>
-      <c r="K20" s="49" t="s">
-        <v>84</v>
+      <c r="H20" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="I20" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="J20" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="K20" s="22" t="s">
+        <v>88</v>
       </c>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -9867,25 +9714,25 @@
     </row>
     <row r="21">
       <c r="A21" s="1"/>
-      <c r="B21" s="46"/>
+      <c r="B21" s="47"/>
       <c r="C21" s="40"/>
       <c r="D21" s="40"/>
       <c r="E21" s="40"/>
       <c r="F21" s="40"/>
-      <c r="G21" s="47">
+      <c r="G21" s="49">
         <v>8.0</v>
       </c>
-      <c r="H21" s="48" t="s">
-        <v>85</v>
-      </c>
-      <c r="I21" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="J21" s="48" t="s">
-        <v>40</v>
-      </c>
-      <c r="K21" s="49" t="s">
-        <v>87</v>
+      <c r="H21" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="I21" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="J21" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="K21" s="22" t="s">
+        <v>91</v>
       </c>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -9906,16 +9753,16 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="46"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="28"/>
-      <c r="I22" s="28"/>
-      <c r="J22" s="28"/>
-      <c r="K22" s="28"/>
+      <c r="B22" s="47"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="29"/>
+      <c r="I22" s="29"/>
+      <c r="J22" s="29"/>
+      <c r="K22" s="29"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
@@ -9935,33 +9782,33 @@
     </row>
     <row r="23">
       <c r="A23" s="1"/>
-      <c r="B23" s="46"/>
-      <c r="C23" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="G23" s="33">
+      <c r="B23" s="47"/>
+      <c r="C23" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="G23" s="31">
         <v>1.0</v>
       </c>
-      <c r="H23" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="I23" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="J23" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="K23" s="18" t="s">
-        <v>100</v>
+      <c r="H23" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="I23" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="J23" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="K23" s="21" t="s">
+        <v>115</v>
       </c>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
@@ -9982,25 +9829,25 @@
     </row>
     <row r="24">
       <c r="A24" s="1"/>
-      <c r="B24" s="46"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="16">
+      <c r="B24" s="47"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="18">
         <v>2.0</v>
       </c>
-      <c r="H24" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="I24" s="17" t="s">
+      <c r="H24" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="I24" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="J24" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="J24" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="K24" s="18" t="s">
-        <v>101</v>
+      <c r="K24" s="21" t="s">
+        <v>116</v>
       </c>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
@@ -10021,25 +9868,25 @@
     </row>
     <row r="25">
       <c r="A25" s="1"/>
-      <c r="B25" s="46"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="16">
+      <c r="B25" s="47"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="18">
         <v>3.0</v>
       </c>
-      <c r="H25" s="17" t="s">
+      <c r="H25" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="I25" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="J25" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="I25" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="J25" s="18" t="s">
+      <c r="K25" s="21" t="s">
         <v>52</v>
-      </c>
-      <c r="K25" s="18" t="s">
-        <v>53</v>
       </c>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -10060,16 +9907,16 @@
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="46"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="28"/>
-      <c r="J26" s="28"/>
-      <c r="K26" s="28"/>
+      <c r="B26" s="47"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29"/>
+      <c r="K26" s="29"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
@@ -10089,33 +9936,33 @@
     </row>
     <row r="27">
       <c r="A27" s="1"/>
-      <c r="B27" s="46"/>
+      <c r="B27" s="47"/>
       <c r="C27" s="52" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="D27" s="53" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E27" s="53" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="F27" s="53" t="s">
-        <v>97</v>
-      </c>
-      <c r="G27" s="33">
+        <v>112</v>
+      </c>
+      <c r="G27" s="31">
         <v>1.0</v>
       </c>
-      <c r="H27" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="I27" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="J27" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="K27" s="18" t="s">
-        <v>100</v>
+      <c r="H27" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="I27" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="J27" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="K27" s="21" t="s">
+        <v>115</v>
       </c>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -10136,25 +9983,25 @@
     </row>
     <row r="28">
       <c r="A28" s="1"/>
-      <c r="B28" s="46"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="16">
+      <c r="B28" s="47"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="18">
         <v>2.0</v>
       </c>
-      <c r="H28" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="I28" s="17" t="s">
+      <c r="H28" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="I28" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="J28" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="J28" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="K28" s="18" t="s">
-        <v>101</v>
+      <c r="K28" s="21" t="s">
+        <v>116</v>
       </c>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -10175,25 +10022,25 @@
     </row>
     <row r="29">
       <c r="A29" s="1"/>
-      <c r="B29" s="46"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="16">
+      <c r="B29" s="47"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="18">
         <v>3.0</v>
       </c>
-      <c r="H29" s="17" t="s">
+      <c r="H29" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="I29" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="J29" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="I29" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="J29" s="18" t="s">
+      <c r="K29" s="21" t="s">
         <v>52</v>
-      </c>
-      <c r="K29" s="18" t="s">
-        <v>53</v>
       </c>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -10214,16 +10061,16 @@
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="46"/>
+      <c r="B30" s="47"/>
       <c r="C30" s="54"/>
       <c r="D30" s="54"/>
       <c r="E30" s="54"/>
       <c r="F30" s="54"/>
-      <c r="G30" s="29"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="28"/>
-      <c r="J30" s="28"/>
-      <c r="K30" s="28"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="29"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="29"/>
+      <c r="K30" s="29"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
@@ -10243,33 +10090,33 @@
     </row>
     <row r="31">
       <c r="A31" s="1"/>
-      <c r="B31" s="46"/>
+      <c r="B31" s="47"/>
       <c r="C31" s="55" t="s">
-        <v>104</v>
-      </c>
-      <c r="D31" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="E31" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="F31" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="G31" s="16">
+        <v>119</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="F31" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="G31" s="18">
         <v>1.0</v>
       </c>
-      <c r="H31" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="I31" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="J31" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="K31" s="18" t="s">
-        <v>110</v>
+      <c r="H31" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="I31" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="J31" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="K31" s="21" t="s">
+        <v>125</v>
       </c>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -10290,25 +10137,25 @@
     </row>
     <row r="32">
       <c r="A32" s="1"/>
-      <c r="B32" s="46"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="16">
+      <c r="B32" s="47"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="18">
         <v>2.0</v>
       </c>
-      <c r="H32" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="I32" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="J32" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="K32" s="18" t="s">
-        <v>94</v>
+      <c r="H32" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="I32" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="J32" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="K32" s="21" t="s">
+        <v>128</v>
       </c>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -10329,25 +10176,25 @@
     </row>
     <row r="33">
       <c r="A33" s="1"/>
-      <c r="B33" s="46"/>
-      <c r="C33" s="22"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="16">
+      <c r="B33" s="47"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="18">
         <v>3.0</v>
       </c>
-      <c r="H33" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="I33" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="J33" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="K33" s="18" t="s">
-        <v>116</v>
+      <c r="H33" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="I33" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="J33" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="K33" s="21" t="s">
+        <v>132</v>
       </c>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
@@ -10368,25 +10215,25 @@
     </row>
     <row r="34">
       <c r="A34" s="1"/>
-      <c r="B34" s="46"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="16">
+      <c r="B34" s="47"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="18">
         <v>4.0</v>
       </c>
-      <c r="H34" s="26" t="s">
-        <v>117</v>
-      </c>
-      <c r="I34" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="J34" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="K34" s="18" t="s">
-        <v>37</v>
+      <c r="H34" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="I34" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="J34" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="K34" s="21" t="s">
+        <v>85</v>
       </c>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
@@ -10407,16 +10254,16 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="1"/>
-      <c r="B35" s="46"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="29"/>
-      <c r="H35" s="28"/>
-      <c r="I35" s="28"/>
-      <c r="J35" s="28"/>
-      <c r="K35" s="28"/>
+      <c r="B35" s="47"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="29"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="29"/>
+      <c r="I35" s="29"/>
+      <c r="J35" s="29"/>
+      <c r="K35" s="29"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
       <c r="N35" s="1"/>
@@ -10436,33 +10283,33 @@
     </row>
     <row r="36">
       <c r="A36" s="1"/>
-      <c r="B36" s="46"/>
+      <c r="B36" s="47"/>
       <c r="C36" s="52" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="D36" s="53" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E36" s="53" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="F36" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="G36" s="16">
+        <v>137</v>
+      </c>
+      <c r="G36" s="18">
         <v>1.0</v>
       </c>
-      <c r="H36" s="26" t="s">
-        <v>122</v>
-      </c>
-      <c r="I36" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="J36" s="24" t="s">
-        <v>124</v>
-      </c>
-      <c r="K36" s="18" t="s">
-        <v>125</v>
+      <c r="H36" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="I36" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="J36" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="K36" s="21" t="s">
+        <v>141</v>
       </c>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
@@ -10483,25 +10330,25 @@
     </row>
     <row r="37">
       <c r="A37" s="1"/>
-      <c r="B37" s="46"/>
-      <c r="C37" s="22"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="22"/>
-      <c r="F37" s="22"/>
+      <c r="B37" s="47"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="24"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
       <c r="G37" s="56">
         <v>2.0</v>
       </c>
-      <c r="H37" s="34" t="s">
-        <v>126</v>
-      </c>
-      <c r="I37" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="J37" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="K37" s="18" t="s">
-        <v>125</v>
+      <c r="H37" s="32" t="s">
+        <v>142</v>
+      </c>
+      <c r="I37" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="J37" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="K37" s="21" t="s">
+        <v>141</v>
       </c>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
@@ -10522,25 +10369,25 @@
     </row>
     <row r="38">
       <c r="A38" s="1"/>
-      <c r="B38" s="46"/>
-      <c r="C38" s="22"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="22"/>
-      <c r="F38" s="22"/>
+      <c r="B38" s="47"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="24"/>
+      <c r="E38" s="24"/>
+      <c r="F38" s="24"/>
       <c r="G38" s="56">
         <v>3.0</v>
       </c>
-      <c r="H38" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="I38" s="34" t="s">
-        <v>129</v>
-      </c>
-      <c r="J38" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="K38" s="18" t="s">
-        <v>130</v>
+      <c r="H38" s="32" t="s">
+        <v>144</v>
+      </c>
+      <c r="I38" s="32" t="s">
+        <v>145</v>
+      </c>
+      <c r="J38" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="K38" s="21" t="s">
+        <v>146</v>
       </c>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
@@ -10561,25 +10408,25 @@
     </row>
     <row r="39">
       <c r="A39" s="1"/>
-      <c r="B39" s="46"/>
-      <c r="C39" s="22"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="22"/>
-      <c r="F39" s="22"/>
+      <c r="B39" s="47"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="24"/>
       <c r="G39" s="56">
         <v>4.0</v>
       </c>
-      <c r="H39" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="I39" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="J39" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="K39" s="24" t="s">
-        <v>133</v>
+      <c r="H39" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="I39" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="J39" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="K39" s="48" t="s">
+        <v>149</v>
       </c>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -10600,7 +10447,7 @@
     </row>
     <row r="40">
       <c r="A40" s="1"/>
-      <c r="B40" s="46"/>
+      <c r="B40" s="47"/>
       <c r="C40" s="40"/>
       <c r="D40" s="40"/>
       <c r="E40" s="40"/>
@@ -10608,17 +10455,17 @@
       <c r="G40" s="56">
         <v>5.0</v>
       </c>
-      <c r="H40" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="I40" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="J40" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="K40" s="18" t="s">
-        <v>137</v>
+      <c r="H40" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="I40" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="J40" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="K40" s="21" t="s">
+        <v>153</v>
       </c>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
@@ -10639,16 +10486,16 @@
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="46"/>
+      <c r="B41" s="47"/>
       <c r="C41" s="57"/>
-      <c r="D41" s="28"/>
-      <c r="E41" s="28"/>
-      <c r="F41" s="28"/>
-      <c r="G41" s="29"/>
-      <c r="H41" s="28"/>
-      <c r="I41" s="28"/>
-      <c r="J41" s="28"/>
-      <c r="K41" s="28"/>
+      <c r="D41" s="29"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="29"/>
+      <c r="G41" s="30"/>
+      <c r="H41" s="29"/>
+      <c r="I41" s="29"/>
+      <c r="J41" s="29"/>
+      <c r="K41" s="29"/>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
       <c r="N41" s="1"/>
@@ -10668,33 +10515,33 @@
     </row>
     <row r="42">
       <c r="A42" s="1"/>
-      <c r="B42" s="46"/>
+      <c r="B42" s="47"/>
       <c r="C42" s="58" t="s">
+        <v>154</v>
+      </c>
+      <c r="D42" s="59" t="s">
+        <v>93</v>
+      </c>
+      <c r="E42" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="F42" s="59" t="s">
+        <v>137</v>
+      </c>
+      <c r="G42" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="H42" s="27" t="s">
         <v>138</v>
       </c>
-      <c r="D42" s="59" t="s">
-        <v>89</v>
-      </c>
-      <c r="E42" s="59" t="s">
-        <v>120</v>
-      </c>
-      <c r="F42" s="59" t="s">
-        <v>121</v>
-      </c>
-      <c r="G42" s="16">
-        <v>1.0</v>
-      </c>
-      <c r="H42" s="26" t="s">
-        <v>122</v>
-      </c>
-      <c r="I42" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="J42" s="24" t="s">
-        <v>124</v>
-      </c>
-      <c r="K42" s="18" t="s">
-        <v>125</v>
+      <c r="I42" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="J42" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="K42" s="21" t="s">
+        <v>141</v>
       </c>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
@@ -10715,25 +10562,25 @@
     </row>
     <row r="43">
       <c r="A43" s="1"/>
-      <c r="B43" s="46"/>
-      <c r="C43" s="22"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="22"/>
-      <c r="F43" s="22"/>
+      <c r="B43" s="47"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="24"/>
+      <c r="E43" s="24"/>
+      <c r="F43" s="24"/>
       <c r="G43" s="56">
         <v>2.0</v>
       </c>
-      <c r="H43" s="34" t="s">
-        <v>126</v>
-      </c>
-      <c r="I43" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="J43" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="K43" s="18" t="s">
-        <v>125</v>
+      <c r="H43" s="32" t="s">
+        <v>142</v>
+      </c>
+      <c r="I43" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="J43" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="K43" s="21" t="s">
+        <v>141</v>
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
@@ -10754,25 +10601,25 @@
     </row>
     <row r="44">
       <c r="A44" s="1"/>
-      <c r="B44" s="46"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="22"/>
-      <c r="E44" s="22"/>
-      <c r="F44" s="22"/>
+      <c r="B44" s="47"/>
+      <c r="C44" s="24"/>
+      <c r="D44" s="24"/>
+      <c r="E44" s="24"/>
+      <c r="F44" s="24"/>
       <c r="G44" s="56">
         <v>3.0</v>
       </c>
-      <c r="H44" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="I44" s="34" t="s">
+      <c r="H44" s="32" t="s">
+        <v>144</v>
+      </c>
+      <c r="I44" s="32" t="s">
+        <v>156</v>
+      </c>
+      <c r="J44" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="J44" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="K44" s="18" t="s">
-        <v>130</v>
+      <c r="K44" s="21" t="s">
+        <v>146</v>
       </c>
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
@@ -10793,25 +10640,25 @@
     </row>
     <row r="45">
       <c r="A45" s="1"/>
-      <c r="B45" s="46"/>
-      <c r="C45" s="22"/>
-      <c r="D45" s="22"/>
-      <c r="E45" s="22"/>
-      <c r="F45" s="22"/>
+      <c r="B45" s="47"/>
+      <c r="C45" s="24"/>
+      <c r="D45" s="24"/>
+      <c r="E45" s="24"/>
+      <c r="F45" s="24"/>
       <c r="G45" s="56">
         <v>4.0</v>
       </c>
-      <c r="H45" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="I45" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="J45" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="K45" s="24" t="s">
-        <v>133</v>
+      <c r="H45" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="I45" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="J45" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="K45" s="48" t="s">
+        <v>149</v>
       </c>
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
@@ -10832,7 +10679,7 @@
     </row>
     <row r="46">
       <c r="A46" s="1"/>
-      <c r="B46" s="46"/>
+      <c r="B46" s="47"/>
       <c r="C46" s="40"/>
       <c r="D46" s="40"/>
       <c r="E46" s="40"/>
@@ -10840,17 +10687,17 @@
       <c r="G46" s="56">
         <v>5.0</v>
       </c>
-      <c r="H46" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="I46" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="J46" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="K46" s="18" t="s">
-        <v>137</v>
+      <c r="H46" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="I46" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="J46" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="K46" s="21" t="s">
+        <v>153</v>
       </c>
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
@@ -10871,16 +10718,16 @@
     </row>
     <row r="47">
       <c r="A47" s="1"/>
-      <c r="B47" s="46"/>
+      <c r="B47" s="47"/>
       <c r="C47" s="57"/>
-      <c r="D47" s="28"/>
-      <c r="E47" s="28"/>
-      <c r="F47" s="28"/>
-      <c r="G47" s="29"/>
-      <c r="H47" s="28"/>
-      <c r="I47" s="28"/>
-      <c r="J47" s="28"/>
-      <c r="K47" s="28"/>
+      <c r="D47" s="29"/>
+      <c r="E47" s="29"/>
+      <c r="F47" s="29"/>
+      <c r="G47" s="30"/>
+      <c r="H47" s="29"/>
+      <c r="I47" s="29"/>
+      <c r="J47" s="29"/>
+      <c r="K47" s="29"/>
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
       <c r="N47" s="1"/>
@@ -10900,33 +10747,33 @@
     </row>
     <row r="48">
       <c r="A48" s="1"/>
-      <c r="B48" s="46"/>
+      <c r="B48" s="47"/>
       <c r="C48" s="58" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="D48" s="59" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E48" s="60" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="F48" s="60" t="s">
-        <v>143</v>
-      </c>
-      <c r="G48" s="16">
+        <v>159</v>
+      </c>
+      <c r="G48" s="18">
         <v>1.0</v>
       </c>
       <c r="H48" s="61" t="s">
-        <v>144</v>
-      </c>
-      <c r="I48" s="23" t="s">
-        <v>145</v>
-      </c>
-      <c r="J48" s="48" t="s">
-        <v>146</v>
-      </c>
-      <c r="K48" s="49" t="s">
-        <v>147</v>
+        <v>160</v>
+      </c>
+      <c r="I48" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="J48" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="K48" s="22" t="s">
+        <v>163</v>
       </c>
       <c r="L48" s="1"/>
       <c r="M48" s="1"/>
@@ -10947,25 +10794,25 @@
     </row>
     <row r="49">
       <c r="A49" s="1"/>
-      <c r="B49" s="46"/>
-      <c r="C49" s="22"/>
-      <c r="D49" s="22"/>
-      <c r="E49" s="22"/>
-      <c r="F49" s="22"/>
+      <c r="B49" s="47"/>
+      <c r="C49" s="24"/>
+      <c r="D49" s="24"/>
+      <c r="E49" s="24"/>
+      <c r="F49" s="24"/>
       <c r="G49" s="56">
         <v>2.0</v>
       </c>
-      <c r="H49" s="62" t="s">
-        <v>148</v>
-      </c>
-      <c r="I49" s="23" t="s">
-        <v>145</v>
-      </c>
-      <c r="J49" s="48" t="s">
-        <v>146</v>
-      </c>
-      <c r="K49" s="49" t="s">
-        <v>149</v>
+      <c r="H49" s="39" t="s">
+        <v>164</v>
+      </c>
+      <c r="I49" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="J49" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="K49" s="22" t="s">
+        <v>166</v>
       </c>
       <c r="L49" s="1"/>
       <c r="M49" s="1"/>
@@ -10986,7 +10833,7 @@
     </row>
     <row r="50">
       <c r="A50" s="1"/>
-      <c r="B50" s="63"/>
+      <c r="B50" s="62"/>
       <c r="C50" s="40"/>
       <c r="D50" s="40"/>
       <c r="E50" s="40"/>
@@ -10994,17 +10841,17 @@
       <c r="G50" s="56">
         <v>3.0</v>
       </c>
-      <c r="H50" s="62" t="s">
-        <v>150</v>
-      </c>
-      <c r="I50" s="23" t="s">
-        <v>151</v>
-      </c>
-      <c r="J50" s="49" t="s">
-        <v>146</v>
-      </c>
-      <c r="K50" s="49" t="s">
-        <v>152</v>
+      <c r="H50" s="39" t="s">
+        <v>167</v>
+      </c>
+      <c r="I50" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="J50" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="K50" s="22" t="s">
+        <v>169</v>
       </c>
       <c r="L50" s="1"/>
       <c r="M50" s="1"/>
@@ -11025,7 +10872,7 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="1"/>
-      <c r="B51" s="64"/>
+      <c r="B51" s="33"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -17484,7 +17331,7 @@
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="44" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
@@ -17587,7 +17434,7 @@
       <c r="K4" s="9"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1" t="s">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
@@ -17598,7 +17445,7 @@
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
       <c r="V4" s="1" t="s">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
@@ -17608,35 +17455,35 @@
     </row>
     <row r="5" ht="44.25" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="E5" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="F5" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="G5" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="H5" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="I5" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="J5" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="K5" s="11" t="s">
         <v>12</v>
-      </c>
-      <c r="J5" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>14</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -17657,37 +17504,37 @@
     </row>
     <row r="6">
       <c r="A6" s="1"/>
-      <c r="B6" s="65" t="s">
-        <v>154</v>
+      <c r="B6" s="63" t="s">
+        <v>171</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="D6" s="55" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="E6" s="55" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="F6" s="55" t="s">
-        <v>158</v>
-      </c>
-      <c r="G6" s="16">
+        <v>175</v>
+      </c>
+      <c r="G6" s="18">
         <v>1.0</v>
       </c>
-      <c r="H6" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="I6" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="J6" s="49" t="s">
-        <v>161</v>
-      </c>
-      <c r="K6" s="49" t="s">
-        <v>162</v>
-      </c>
-      <c r="L6" s="19"/>
+      <c r="H6" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="I6" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="J6" s="22" t="s">
+        <v>178</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="L6" s="46"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
@@ -17706,25 +17553,25 @@
     </row>
     <row r="7">
       <c r="A7" s="1"/>
-      <c r="B7" s="22"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="16">
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="18">
         <v>2.0</v>
       </c>
-      <c r="H7" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="I7" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="J7" s="49" t="s">
-        <v>165</v>
-      </c>
-      <c r="K7" s="49" t="s">
-        <v>166</v>
+      <c r="H7" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="J7" s="22" t="s">
+        <v>182</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>183</v>
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
@@ -17745,25 +17592,25 @@
     </row>
     <row r="8">
       <c r="A8" s="1"/>
-      <c r="B8" s="22"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="16">
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="18">
         <v>3.0</v>
       </c>
-      <c r="H8" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="I8" s="23" t="s">
-        <v>168</v>
-      </c>
-      <c r="J8" s="48" t="s">
-        <v>161</v>
-      </c>
-      <c r="K8" s="49" t="s">
-        <v>169</v>
+      <c r="H8" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="I8" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="J8" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>186</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -17784,25 +17631,25 @@
     </row>
     <row r="9">
       <c r="A9" s="1"/>
-      <c r="B9" s="22"/>
+      <c r="B9" s="24"/>
       <c r="C9" s="40"/>
       <c r="D9" s="40"/>
       <c r="E9" s="40"/>
       <c r="F9" s="40"/>
-      <c r="G9" s="16">
+      <c r="G9" s="18">
         <v>4.0</v>
       </c>
       <c r="H9" s="61" t="s">
-        <v>170</v>
-      </c>
-      <c r="I9" s="23" t="s">
-        <v>171</v>
-      </c>
-      <c r="J9" s="49" t="s">
-        <v>161</v>
-      </c>
-      <c r="K9" s="49" t="s">
-        <v>172</v>
+        <v>187</v>
+      </c>
+      <c r="I9" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="J9" s="22" t="s">
+        <v>178</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>189</v>
       </c>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -17823,16 +17670,16 @@
     </row>
     <row r="10">
       <c r="A10" s="1"/>
-      <c r="B10" s="22"/>
+      <c r="B10" s="24"/>
       <c r="C10" s="50"/>
       <c r="D10" s="50"/>
       <c r="E10" s="50"/>
       <c r="F10" s="50"/>
-      <c r="G10" s="29"/>
+      <c r="G10" s="30"/>
       <c r="H10" s="51"/>
-      <c r="I10" s="28"/>
-      <c r="J10" s="28"/>
-      <c r="K10" s="28"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="29"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
@@ -17852,33 +17699,33 @@
     </row>
     <row r="11">
       <c r="A11" s="1"/>
-      <c r="B11" s="22"/>
+      <c r="B11" s="24"/>
       <c r="C11" s="55" t="s">
+        <v>190</v>
+      </c>
+      <c r="D11" s="55" t="s">
         <v>173</v>
       </c>
-      <c r="D11" s="55" t="s">
-        <v>156</v>
-      </c>
       <c r="E11" s="55" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="F11" s="55" t="s">
-        <v>175</v>
-      </c>
-      <c r="G11" s="16">
+        <v>192</v>
+      </c>
+      <c r="G11" s="18">
         <v>1.0</v>
       </c>
-      <c r="H11" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="I11" s="23" t="s">
+      <c r="H11" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="J11" s="49" t="s">
-        <v>161</v>
-      </c>
-      <c r="K11" s="49" t="s">
-        <v>162</v>
+      <c r="I11" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="J11" s="22" t="s">
+        <v>178</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>179</v>
       </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -17899,25 +17746,25 @@
     </row>
     <row r="12">
       <c r="A12" s="1"/>
-      <c r="B12" s="22"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="16">
+      <c r="B12" s="24"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="18">
         <v>2.0</v>
       </c>
-      <c r="H12" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="I12" s="23" t="s">
-        <v>177</v>
-      </c>
-      <c r="J12" s="49" t="s">
-        <v>165</v>
-      </c>
-      <c r="K12" s="49" t="s">
-        <v>166</v>
+      <c r="H12" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="I12" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="J12" s="22" t="s">
+        <v>182</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>183</v>
       </c>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
@@ -17938,25 +17785,25 @@
     </row>
     <row r="13">
       <c r="A13" s="1"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="16">
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="18">
         <v>3.0</v>
       </c>
-      <c r="H13" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="I13" s="23" t="s">
-        <v>168</v>
-      </c>
-      <c r="J13" s="48" t="s">
-        <v>161</v>
-      </c>
-      <c r="K13" s="49" t="s">
-        <v>169</v>
+      <c r="H13" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="I13" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="J13" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="K13" s="22" t="s">
+        <v>186</v>
       </c>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -17977,25 +17824,25 @@
     </row>
     <row r="14">
       <c r="A14" s="1"/>
-      <c r="B14" s="22"/>
+      <c r="B14" s="24"/>
       <c r="C14" s="40"/>
       <c r="D14" s="40"/>
       <c r="E14" s="40"/>
       <c r="F14" s="40"/>
-      <c r="G14" s="16">
+      <c r="G14" s="18">
         <v>4.0</v>
       </c>
       <c r="H14" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="I14" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="J14" s="22" t="s">
         <v>178</v>
       </c>
-      <c r="I14" s="23" t="s">
-        <v>179</v>
-      </c>
-      <c r="J14" s="49" t="s">
-        <v>161</v>
-      </c>
-      <c r="K14" s="49" t="s">
-        <v>180</v>
+      <c r="K14" s="22" t="s">
+        <v>197</v>
       </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -18016,16 +17863,16 @@
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="1"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="28"/>
-      <c r="J15" s="28"/>
-      <c r="K15" s="28"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="29"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
@@ -18045,33 +17892,33 @@
     </row>
     <row r="16">
       <c r="A16" s="1"/>
-      <c r="B16" s="22"/>
+      <c r="B16" s="24"/>
       <c r="C16" s="55" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="D16" s="55" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E16" s="55" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="F16" s="55" t="s">
-        <v>183</v>
-      </c>
-      <c r="G16" s="16">
+        <v>200</v>
+      </c>
+      <c r="G16" s="18">
         <v>1.0</v>
       </c>
-      <c r="H16" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="I16" s="23" t="s">
-        <v>184</v>
-      </c>
-      <c r="J16" s="49" t="s">
-        <v>185</v>
-      </c>
-      <c r="K16" s="49" t="s">
-        <v>186</v>
+      <c r="H16" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="I16" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="J16" s="22" t="s">
+        <v>202</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>203</v>
       </c>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -18092,25 +17939,25 @@
     </row>
     <row r="17">
       <c r="A17" s="1"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="16">
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="18">
         <v>2.0</v>
       </c>
-      <c r="H17" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="I17" s="23" t="s">
-        <v>187</v>
-      </c>
-      <c r="J17" s="49" t="s">
-        <v>165</v>
-      </c>
-      <c r="K17" s="49" t="s">
-        <v>166</v>
+      <c r="H17" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="I17" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="J17" s="22" t="s">
+        <v>182</v>
+      </c>
+      <c r="K17" s="22" t="s">
+        <v>183</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -18131,25 +17978,25 @@
     </row>
     <row r="18">
       <c r="A18" s="1"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="16">
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="18">
         <v>3.0</v>
       </c>
-      <c r="H18" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="I18" s="23" t="s">
-        <v>188</v>
-      </c>
-      <c r="J18" s="48" t="s">
-        <v>161</v>
-      </c>
-      <c r="K18" s="49" t="s">
-        <v>169</v>
+      <c r="H18" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="I18" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="J18" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="K18" s="22" t="s">
+        <v>186</v>
       </c>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -18175,20 +18022,20 @@
       <c r="D19" s="40"/>
       <c r="E19" s="40"/>
       <c r="F19" s="40"/>
-      <c r="G19" s="16">
+      <c r="G19" s="18">
         <v>4.0</v>
       </c>
       <c r="H19" s="61" t="s">
-        <v>189</v>
-      </c>
-      <c r="I19" s="23" t="s">
-        <v>190</v>
-      </c>
-      <c r="J19" s="49" t="s">
-        <v>161</v>
-      </c>
-      <c r="K19" s="49" t="s">
-        <v>191</v>
+        <v>206</v>
+      </c>
+      <c r="I19" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="J19" s="22" t="s">
+        <v>178</v>
+      </c>
+      <c r="K19" s="22" t="s">
+        <v>208</v>
       </c>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -18209,11 +18056,11 @@
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="1"/>
-      <c r="B20" s="64"/>
-      <c r="C20" s="64"/>
-      <c r="D20" s="64"/>
-      <c r="E20" s="64"/>
-      <c r="F20" s="64"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -24703,7 +24550,7 @@
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="44" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
@@ -24806,7 +24653,7 @@
       <c r="K4" s="9"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1" t="s">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
@@ -24817,7 +24664,7 @@
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
       <c r="V4" s="1" t="s">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
@@ -24827,35 +24674,35 @@
     </row>
     <row r="5" ht="44.25" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="E5" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="F5" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="G5" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="H5" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="I5" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="J5" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="K5" s="11" t="s">
         <v>12</v>
-      </c>
-      <c r="J5" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>14</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -24876,37 +24723,37 @@
     </row>
     <row r="6">
       <c r="A6" s="1"/>
-      <c r="B6" s="66" t="s">
-        <v>193</v>
+      <c r="B6" s="64" t="s">
+        <v>210</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="D6" s="55" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="E6" s="55" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="F6" s="55" t="s">
-        <v>196</v>
-      </c>
-      <c r="G6" s="16">
+        <v>213</v>
+      </c>
+      <c r="G6" s="18">
         <v>1.0</v>
       </c>
-      <c r="H6" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="I6" s="23" t="s">
-        <v>198</v>
-      </c>
-      <c r="J6" s="49" t="s">
-        <v>199</v>
-      </c>
-      <c r="K6" s="49" t="s">
-        <v>200</v>
-      </c>
-      <c r="L6" s="19"/>
+      <c r="H6" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="I6" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="J6" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>217</v>
+      </c>
+      <c r="L6" s="46"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
@@ -24925,25 +24772,25 @@
     </row>
     <row r="7">
       <c r="A7" s="1"/>
-      <c r="B7" s="46"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="16">
+      <c r="B7" s="47"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="18">
         <v>2.0</v>
       </c>
-      <c r="H7" s="23" t="s">
-        <v>201</v>
-      </c>
-      <c r="I7" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="J7" s="49" t="s">
-        <v>199</v>
-      </c>
-      <c r="K7" s="49" t="s">
-        <v>203</v>
+      <c r="H7" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="J7" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>220</v>
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
@@ -24964,25 +24811,25 @@
     </row>
     <row r="8">
       <c r="A8" s="1"/>
-      <c r="B8" s="46"/>
+      <c r="B8" s="47"/>
       <c r="C8" s="40"/>
       <c r="D8" s="40"/>
       <c r="E8" s="40"/>
       <c r="F8" s="40"/>
-      <c r="G8" s="16">
+      <c r="G8" s="18">
         <v>3.0</v>
       </c>
-      <c r="H8" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="I8" s="23" t="s">
-        <v>205</v>
-      </c>
-      <c r="J8" s="48" t="s">
-        <v>199</v>
-      </c>
-      <c r="K8" s="49" t="s">
-        <v>206</v>
+      <c r="H8" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="I8" s="20" t="s">
+        <v>222</v>
+      </c>
+      <c r="J8" s="25" t="s">
+        <v>216</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>223</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -25003,16 +24850,16 @@
     </row>
     <row r="9">
       <c r="A9" s="1"/>
-      <c r="B9" s="46"/>
+      <c r="B9" s="47"/>
       <c r="C9" s="50"/>
       <c r="D9" s="50"/>
       <c r="E9" s="50"/>
       <c r="F9" s="50"/>
-      <c r="G9" s="29"/>
+      <c r="G9" s="30"/>
       <c r="H9" s="51"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="28"/>
-      <c r="K9" s="28"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="29"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
@@ -25032,33 +24879,33 @@
     </row>
     <row r="10">
       <c r="A10" s="1"/>
-      <c r="B10" s="46"/>
+      <c r="B10" s="47"/>
       <c r="C10" s="55" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="D10" s="55" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="E10" s="55" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="F10" s="55" t="s">
-        <v>209</v>
-      </c>
-      <c r="G10" s="16">
+        <v>226</v>
+      </c>
+      <c r="G10" s="18">
         <v>1.0</v>
       </c>
-      <c r="H10" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="I10" s="23" t="s">
-        <v>198</v>
-      </c>
-      <c r="J10" s="49" t="s">
-        <v>199</v>
-      </c>
-      <c r="K10" s="49" t="s">
-        <v>210</v>
+      <c r="H10" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="I10" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="J10" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>227</v>
       </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -25079,25 +24926,25 @@
     </row>
     <row r="11">
       <c r="A11" s="1"/>
-      <c r="B11" s="46"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="16">
+      <c r="B11" s="47"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="18">
         <v>2.0</v>
       </c>
-      <c r="H11" s="23" t="s">
-        <v>201</v>
-      </c>
-      <c r="I11" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="J11" s="49" t="s">
-        <v>199</v>
-      </c>
-      <c r="K11" s="49" t="s">
-        <v>203</v>
+      <c r="H11" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="I11" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="J11" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>220</v>
       </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -25118,25 +24965,25 @@
     </row>
     <row r="12">
       <c r="A12" s="1"/>
-      <c r="B12" s="46"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="16">
+      <c r="B12" s="47"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="18">
         <v>3.0</v>
       </c>
-      <c r="H12" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="I12" s="23" t="s">
-        <v>205</v>
-      </c>
-      <c r="J12" s="48" t="s">
-        <v>199</v>
-      </c>
-      <c r="K12" s="49" t="s">
-        <v>206</v>
+      <c r="H12" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="I12" s="20" t="s">
+        <v>222</v>
+      </c>
+      <c r="J12" s="25" t="s">
+        <v>216</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>223</v>
       </c>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
@@ -25157,25 +25004,25 @@
     </row>
     <row r="13">
       <c r="A13" s="1"/>
-      <c r="B13" s="46"/>
+      <c r="B13" s="47"/>
       <c r="C13" s="40"/>
       <c r="D13" s="40"/>
       <c r="E13" s="40"/>
       <c r="F13" s="40"/>
-      <c r="G13" s="16">
+      <c r="G13" s="18">
         <v>4.0</v>
       </c>
       <c r="H13" s="61" t="s">
-        <v>211</v>
-      </c>
-      <c r="I13" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="J13" s="48" t="s">
-        <v>199</v>
-      </c>
-      <c r="K13" s="49" t="s">
-        <v>213</v>
+        <v>228</v>
+      </c>
+      <c r="I13" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="J13" s="25" t="s">
+        <v>216</v>
+      </c>
+      <c r="K13" s="22" t="s">
+        <v>230</v>
       </c>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -25196,16 +25043,16 @@
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="1"/>
-      <c r="B14" s="46"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="28"/>
-      <c r="I14" s="28"/>
-      <c r="J14" s="28"/>
-      <c r="K14" s="28"/>
+      <c r="B14" s="47"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="29"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
@@ -25225,33 +25072,33 @@
     </row>
     <row r="15">
       <c r="A15" s="1"/>
-      <c r="B15" s="46"/>
+      <c r="B15" s="47"/>
       <c r="C15" s="55" t="s">
+        <v>231</v>
+      </c>
+      <c r="D15" s="55" t="s">
+        <v>93</v>
+      </c>
+      <c r="E15" s="55" t="s">
+        <v>212</v>
+      </c>
+      <c r="F15" s="55" t="s">
+        <v>232</v>
+      </c>
+      <c r="G15" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="H15" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="D15" s="55" t="s">
-        <v>89</v>
-      </c>
-      <c r="E15" s="55" t="s">
-        <v>195</v>
-      </c>
-      <c r="F15" s="55" t="s">
+      <c r="I15" s="20" t="s">
         <v>215</v>
       </c>
-      <c r="G15" s="16">
-        <v>1.0</v>
-      </c>
-      <c r="H15" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="I15" s="23" t="s">
-        <v>198</v>
-      </c>
-      <c r="J15" s="49" t="s">
-        <v>199</v>
-      </c>
-      <c r="K15" s="49" t="s">
+      <c r="J15" s="22" t="s">
         <v>216</v>
+      </c>
+      <c r="K15" s="22" t="s">
+        <v>233</v>
       </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -25272,25 +25119,25 @@
     </row>
     <row r="16">
       <c r="A16" s="1"/>
-      <c r="B16" s="46"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="16">
+      <c r="B16" s="47"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="18">
         <v>2.0</v>
       </c>
-      <c r="H16" s="23" t="s">
-        <v>201</v>
-      </c>
-      <c r="I16" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="J16" s="49" t="s">
-        <v>199</v>
-      </c>
-      <c r="K16" s="49" t="s">
-        <v>203</v>
+      <c r="H16" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="I16" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="J16" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>220</v>
       </c>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -25311,25 +25158,25 @@
     </row>
     <row r="17">
       <c r="A17" s="1"/>
-      <c r="B17" s="46"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="16">
+      <c r="B17" s="47"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="18">
         <v>3.0</v>
       </c>
-      <c r="H17" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="I17" s="23" t="s">
-        <v>205</v>
-      </c>
-      <c r="J17" s="48" t="s">
-        <v>199</v>
-      </c>
-      <c r="K17" s="49" t="s">
-        <v>206</v>
+      <c r="H17" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="I17" s="20" t="s">
+        <v>222</v>
+      </c>
+      <c r="J17" s="25" t="s">
+        <v>216</v>
+      </c>
+      <c r="K17" s="22" t="s">
+        <v>223</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -25350,25 +25197,25 @@
     </row>
     <row r="18">
       <c r="A18" s="1"/>
-      <c r="B18" s="46"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
+      <c r="B18" s="47"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
       <c r="E18" s="40"/>
       <c r="F18" s="40"/>
-      <c r="G18" s="16">
+      <c r="G18" s="18">
         <v>4.0</v>
       </c>
       <c r="H18" s="61" t="s">
-        <v>211</v>
-      </c>
-      <c r="I18" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="J18" s="48" t="s">
-        <v>199</v>
-      </c>
-      <c r="K18" s="49" t="s">
-        <v>213</v>
+        <v>228</v>
+      </c>
+      <c r="I18" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="J18" s="25" t="s">
+        <v>216</v>
+      </c>
+      <c r="K18" s="22" t="s">
+        <v>230</v>
       </c>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -25389,16 +25236,16 @@
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="46"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="28"/>
-      <c r="K19" s="28"/>
+      <c r="B19" s="47"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="29"/>
+      <c r="I19" s="29"/>
+      <c r="J19" s="29"/>
+      <c r="K19" s="29"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
@@ -25418,33 +25265,33 @@
     </row>
     <row r="20">
       <c r="A20" s="1"/>
-      <c r="B20" s="46"/>
+      <c r="B20" s="47"/>
       <c r="C20" s="52" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="D20" s="52" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E20" s="55" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="F20" s="52" t="s">
-        <v>218</v>
-      </c>
-      <c r="G20" s="16">
+        <v>235</v>
+      </c>
+      <c r="G20" s="18">
         <v>1.0</v>
       </c>
-      <c r="H20" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="I20" s="23" t="s">
-        <v>198</v>
-      </c>
-      <c r="J20" s="49" t="s">
-        <v>199</v>
-      </c>
-      <c r="K20" s="49" t="s">
-        <v>219</v>
+      <c r="H20" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="I20" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="J20" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="K20" s="22" t="s">
+        <v>236</v>
       </c>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -25465,25 +25312,25 @@
     </row>
     <row r="21">
       <c r="A21" s="1"/>
-      <c r="B21" s="46"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="16">
+      <c r="B21" s="47"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="18">
         <v>2.0</v>
       </c>
-      <c r="H21" s="23" t="s">
-        <v>201</v>
-      </c>
-      <c r="I21" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="J21" s="49" t="s">
-        <v>199</v>
-      </c>
-      <c r="K21" s="49" t="s">
-        <v>203</v>
+      <c r="H21" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="I21" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="J21" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="K21" s="22" t="s">
+        <v>220</v>
       </c>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -25504,25 +25351,25 @@
     </row>
     <row r="22">
       <c r="A22" s="1"/>
-      <c r="B22" s="46"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="16">
+      <c r="B22" s="47"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="18">
         <v>3.0</v>
       </c>
-      <c r="H22" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="I22" s="23" t="s">
-        <v>205</v>
-      </c>
-      <c r="J22" s="48" t="s">
-        <v>199</v>
-      </c>
-      <c r="K22" s="49" t="s">
-        <v>206</v>
+      <c r="H22" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="I22" s="20" t="s">
+        <v>222</v>
+      </c>
+      <c r="J22" s="25" t="s">
+        <v>216</v>
+      </c>
+      <c r="K22" s="22" t="s">
+        <v>223</v>
       </c>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -25543,25 +25390,25 @@
     </row>
     <row r="23">
       <c r="A23" s="1"/>
-      <c r="B23" s="46"/>
+      <c r="B23" s="47"/>
       <c r="C23" s="40"/>
       <c r="D23" s="40"/>
       <c r="E23" s="40"/>
       <c r="F23" s="40"/>
-      <c r="G23" s="16">
+      <c r="G23" s="18">
         <v>4.0</v>
       </c>
       <c r="H23" s="61" t="s">
-        <v>211</v>
-      </c>
-      <c r="I23" s="23" t="s">
-        <v>220</v>
-      </c>
-      <c r="J23" s="48" t="s">
-        <v>199</v>
-      </c>
-      <c r="K23" s="49" t="s">
-        <v>213</v>
+        <v>228</v>
+      </c>
+      <c r="I23" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="J23" s="25" t="s">
+        <v>216</v>
+      </c>
+      <c r="K23" s="22" t="s">
+        <v>230</v>
       </c>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
@@ -25582,16 +25429,16 @@
     </row>
     <row r="24">
       <c r="A24" s="1"/>
-      <c r="B24" s="46"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="28"/>
-      <c r="J24" s="28"/>
-      <c r="K24" s="28"/>
+      <c r="B24" s="47"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="29"/>
+      <c r="I24" s="29"/>
+      <c r="J24" s="29"/>
+      <c r="K24" s="29"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
@@ -25611,33 +25458,33 @@
     </row>
     <row r="25">
       <c r="A25" s="1"/>
-      <c r="B25" s="46"/>
+      <c r="B25" s="47"/>
       <c r="C25" s="52" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="D25" s="52" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="E25" s="55" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="F25" s="52" t="s">
-        <v>223</v>
-      </c>
-      <c r="G25" s="16">
+        <v>240</v>
+      </c>
+      <c r="G25" s="18">
         <v>1.0</v>
       </c>
-      <c r="H25" s="23" t="s">
-        <v>224</v>
-      </c>
-      <c r="I25" s="23" t="s">
-        <v>225</v>
-      </c>
-      <c r="J25" s="49" t="s">
-        <v>226</v>
-      </c>
-      <c r="K25" s="49" t="s">
-        <v>227</v>
+      <c r="H25" s="20" t="s">
+        <v>241</v>
+      </c>
+      <c r="I25" s="20" t="s">
+        <v>242</v>
+      </c>
+      <c r="J25" s="22" t="s">
+        <v>243</v>
+      </c>
+      <c r="K25" s="22" t="s">
+        <v>244</v>
       </c>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -25658,25 +25505,25 @@
     </row>
     <row r="26">
       <c r="A26" s="1"/>
-      <c r="B26" s="46"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="16">
+      <c r="B26" s="47"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="18">
         <v>2.0</v>
       </c>
-      <c r="H26" s="23" t="s">
-        <v>228</v>
-      </c>
-      <c r="I26" s="23" t="s">
-        <v>229</v>
-      </c>
-      <c r="J26" s="49" t="s">
-        <v>230</v>
-      </c>
-      <c r="K26" s="49" t="s">
-        <v>231</v>
+      <c r="H26" s="20" t="s">
+        <v>245</v>
+      </c>
+      <c r="I26" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="J26" s="22" t="s">
+        <v>247</v>
+      </c>
+      <c r="K26" s="22" t="s">
+        <v>248</v>
       </c>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -25697,25 +25544,25 @@
     </row>
     <row r="27">
       <c r="A27" s="1"/>
-      <c r="B27" s="46"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="16">
+      <c r="B27" s="47"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="18">
         <v>3.0</v>
       </c>
-      <c r="H27" s="23" t="s">
-        <v>232</v>
-      </c>
-      <c r="I27" s="23" t="s">
-        <v>233</v>
-      </c>
-      <c r="J27" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="K27" s="49" t="s">
-        <v>235</v>
+      <c r="H27" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="I27" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="J27" s="25" t="s">
+        <v>251</v>
+      </c>
+      <c r="K27" s="22" t="s">
+        <v>252</v>
       </c>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -25736,16 +25583,16 @@
     </row>
     <row r="28">
       <c r="A28" s="1"/>
-      <c r="B28" s="63"/>
+      <c r="B28" s="62"/>
       <c r="C28" s="40"/>
       <c r="D28" s="40"/>
       <c r="E28" s="40"/>
       <c r="F28" s="40"/>
-      <c r="G28" s="16"/>
+      <c r="G28" s="18"/>
       <c r="H28" s="61"/>
-      <c r="I28" s="23"/>
-      <c r="J28" s="48"/>
-      <c r="K28" s="49"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="25"/>
+      <c r="K28" s="22"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
@@ -25765,7 +25612,7 @@
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="64"/>
+      <c r="B29" s="33"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
@@ -32241,7 +32088,7 @@
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="44" t="s">
-        <v>192</v>
+        <v>253</v>
       </c>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
@@ -32344,7 +32191,7 @@
       <c r="K4" s="9"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1" t="s">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
@@ -32355,7 +32202,7 @@
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
       <c r="V4" s="1" t="s">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
@@ -32365,35 +32212,35 @@
     </row>
     <row r="5" ht="44.25" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="E5" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="F5" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="G5" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="H5" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="I5" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="J5" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="K5" s="11" t="s">
         <v>12</v>
-      </c>
-      <c r="J5" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>14</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -32414,37 +32261,37 @@
     </row>
     <row r="6">
       <c r="A6" s="1"/>
-      <c r="B6" s="65" t="s">
-        <v>236</v>
+      <c r="B6" s="63" t="s">
+        <v>254</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="D6" s="55" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="E6" s="55" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="F6" s="55" t="s">
-        <v>239</v>
-      </c>
-      <c r="G6" s="16">
+        <v>257</v>
+      </c>
+      <c r="G6" s="18">
         <v>1.0</v>
       </c>
-      <c r="H6" s="23" t="s">
-        <v>240</v>
-      </c>
-      <c r="I6" s="23" t="s">
-        <v>241</v>
-      </c>
-      <c r="J6" s="49" t="s">
-        <v>242</v>
-      </c>
-      <c r="K6" s="49" t="s">
-        <v>243</v>
-      </c>
-      <c r="L6" s="19"/>
+      <c r="H6" s="20" t="s">
+        <v>258</v>
+      </c>
+      <c r="I6" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="J6" s="22" t="s">
+        <v>260</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>261</v>
+      </c>
+      <c r="L6" s="46"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
@@ -32463,25 +32310,25 @@
     </row>
     <row r="7">
       <c r="A7" s="1"/>
-      <c r="B7" s="22"/>
+      <c r="B7" s="24"/>
       <c r="C7" s="40"/>
       <c r="D7" s="40"/>
       <c r="E7" s="40"/>
       <c r="F7" s="40"/>
-      <c r="G7" s="16">
+      <c r="G7" s="18">
         <v>2.0</v>
       </c>
-      <c r="H7" s="23" t="s">
-        <v>244</v>
-      </c>
-      <c r="I7" s="23" t="s">
-        <v>245</v>
-      </c>
-      <c r="J7" s="49" t="s">
-        <v>242</v>
-      </c>
-      <c r="K7" s="49" t="s">
-        <v>246</v>
+      <c r="H7" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="J7" s="22" t="s">
+        <v>260</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>264</v>
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
@@ -32502,16 +32349,16 @@
     </row>
     <row r="8">
       <c r="A8" s="1"/>
-      <c r="B8" s="22"/>
+      <c r="B8" s="24"/>
       <c r="C8" s="50"/>
       <c r="D8" s="50"/>
       <c r="E8" s="50"/>
       <c r="F8" s="50"/>
-      <c r="G8" s="29"/>
+      <c r="G8" s="30"/>
       <c r="H8" s="51"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="28"/>
-      <c r="K8" s="28"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="29"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
@@ -32531,33 +32378,33 @@
     </row>
     <row r="9">
       <c r="A9" s="1"/>
-      <c r="B9" s="22"/>
+      <c r="B9" s="24"/>
       <c r="C9" s="55" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="D9" s="55" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="E9" s="55" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="F9" s="55" t="s">
-        <v>249</v>
-      </c>
-      <c r="G9" s="16">
+        <v>267</v>
+      </c>
+      <c r="G9" s="18">
         <v>1.0</v>
       </c>
-      <c r="H9" s="23" t="s">
-        <v>250</v>
-      </c>
-      <c r="I9" s="23" t="s">
-        <v>251</v>
-      </c>
-      <c r="J9" s="49" t="s">
-        <v>242</v>
-      </c>
-      <c r="K9" s="49" t="s">
-        <v>252</v>
+      <c r="H9" s="20" t="s">
+        <v>268</v>
+      </c>
+      <c r="I9" s="20" t="s">
+        <v>269</v>
+      </c>
+      <c r="J9" s="22" t="s">
+        <v>260</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>270</v>
       </c>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -32578,18 +32425,18 @@
     </row>
     <row r="10">
       <c r="A10" s="1"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="16">
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="18">
         <v>2.0</v>
       </c>
-      <c r="H10" s="23"/>
-      <c r="I10" s="23"/>
-      <c r="J10" s="49"/>
-      <c r="K10" s="49"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="22"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
@@ -32609,18 +32456,18 @@
     </row>
     <row r="11">
       <c r="A11" s="1"/>
-      <c r="B11" s="22"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="16">
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="18">
         <v>3.0</v>
       </c>
-      <c r="H11" s="23"/>
-      <c r="I11" s="23"/>
-      <c r="J11" s="48"/>
-      <c r="K11" s="49"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="22"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
@@ -32640,18 +32487,18 @@
     </row>
     <row r="12">
       <c r="A12" s="1"/>
-      <c r="B12" s="22"/>
+      <c r="B12" s="24"/>
       <c r="C12" s="40"/>
       <c r="D12" s="40"/>
       <c r="E12" s="40"/>
       <c r="F12" s="40"/>
-      <c r="G12" s="16">
+      <c r="G12" s="18">
         <v>4.0</v>
       </c>
       <c r="H12" s="61"/>
-      <c r="I12" s="23"/>
-      <c r="J12" s="48"/>
-      <c r="K12" s="49"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="22"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
@@ -32671,16 +32518,16 @@
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="28"/>
-      <c r="J13" s="28"/>
-      <c r="K13" s="28"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="29"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="29"/>
+      <c r="K13" s="29"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
@@ -32700,33 +32547,33 @@
     </row>
     <row r="14">
       <c r="A14" s="1"/>
-      <c r="B14" s="22"/>
+      <c r="B14" s="24"/>
       <c r="C14" s="55" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="D14" s="55" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="E14" s="55" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="F14" s="55" t="s">
-        <v>255</v>
-      </c>
-      <c r="G14" s="16">
+        <v>273</v>
+      </c>
+      <c r="G14" s="18">
         <v>1.0</v>
       </c>
-      <c r="H14" s="23" t="s">
-        <v>256</v>
-      </c>
-      <c r="I14" s="23" t="s">
-        <v>257</v>
-      </c>
-      <c r="J14" s="49" t="s">
-        <v>242</v>
-      </c>
-      <c r="K14" s="49" t="s">
-        <v>258</v>
+      <c r="H14" s="20" t="s">
+        <v>274</v>
+      </c>
+      <c r="I14" s="20" t="s">
+        <v>275</v>
+      </c>
+      <c r="J14" s="22" t="s">
+        <v>260</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>276</v>
       </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -32752,20 +32599,20 @@
       <c r="D15" s="40"/>
       <c r="E15" s="40"/>
       <c r="F15" s="40"/>
-      <c r="G15" s="16">
+      <c r="G15" s="18">
         <v>2.0</v>
       </c>
-      <c r="H15" s="23" t="s">
-        <v>259</v>
-      </c>
-      <c r="I15" s="23" t="s">
+      <c r="H15" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="I15" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="J15" s="22" t="s">
         <v>260</v>
       </c>
-      <c r="J15" s="49" t="s">
-        <v>242</v>
-      </c>
-      <c r="K15" s="49" t="s">
-        <v>261</v>
+      <c r="K15" s="22" t="s">
+        <v>279</v>
       </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -32786,9 +32633,9 @@
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="1"/>
-      <c r="B16" s="64"/>
-      <c r="C16" s="64"/>
-      <c r="D16" s="64"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
